--- a/01_Excels_Rieles_Pagos/Slot_Parsheet_Teorico.xlsx
+++ b/01_Excels_Rieles_Pagos/Slot_Parsheet_Teorico.xlsx
@@ -573,7 +573,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="5">
-        <v>2000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -581,7 +581,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="5">
-        <v>5000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -589,7 +589,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="9" spans="1:3">
